--- a/tools/importer/reports/import-case-study-page.report.xlsx
+++ b/tools/importer/reports/import-case-study-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,16 +61,49 @@
     <t>https://fiixsoftware.com/cmms/pricing/</t>
   </si>
   <si>
+    <t>resource-center/case-studies/dlg-group.report.json</t>
+  </si>
+  <si>
+    <t>["hero-case-study","columns-media","hero-cta"]</t>
+  </si>
+  <si>
+    <t>resource-center/case-studies/dlg-group</t>
+  </si>
+  <si>
+    <t>case-study-page</t>
+  </si>
+  <si>
+    <t>2026-08-18T13:02:05.951Z</t>
+  </si>
+  <si>
+    <t>Agri-manufacturer to cut downtime by 10% with CMMS | Fiix</t>
+  </si>
+  <si>
+    <t>https://fiixsoftware.com/resource-center/case-studies/dlg-group/</t>
+  </si>
+  <si>
+    <t>resource-center/case-studies/farming-maintenance.report.json</t>
+  </si>
+  <si>
+    <t>["hero-case-study","hero-cta"]</t>
+  </si>
+  <si>
+    <t>resource-center/case-studies/farming-maintenance</t>
+  </si>
+  <si>
+    <t>2026-08-18T13:06:55.772Z</t>
+  </si>
+  <si>
+    <t>Farming Maintenance Case Study I Fiix</t>
+  </si>
+  <si>
+    <t>https://fiixsoftware.com/resource-center/case-studies/farming-maintenance/</t>
+  </si>
+  <si>
     <t>resource-center/case-studies/universal-pure.report.json</t>
   </si>
   <si>
-    <t>["hero-case-study","columns-media","hero-cta"]</t>
-  </si>
-  <si>
     <t>resource-center/case-studies/universal-pure</t>
-  </si>
-  <si>
-    <t>case-study-page</t>
   </si>
   <si>
     <t>2026-08-17T11:49:15.388Z</t>
@@ -468,11 +501,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
@@ -556,6 +588,58 @@
         <v>22</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-case-study-page.report.xlsx
+++ b/tools/importer/reports/import-case-study-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>_reportFile</t>
   </si>
@@ -80,6 +80,21 @@
   </si>
   <si>
     <t>https://fiixsoftware.com/resource-center/case-studies/dlg-group/</t>
+  </si>
+  <si>
+    <t>resource-center/case-studies/edms-consultants.report.json</t>
+  </si>
+  <si>
+    <t>resource-center/case-studies/edms-consultants</t>
+  </si>
+  <si>
+    <t>2026-08-18T13:43:44.138Z</t>
+  </si>
+  <si>
+    <t>EDMS Consultants: A Maintenance Case Study | Fiix CMMS</t>
+  </si>
+  <si>
+    <t>https://fiixsoftware.com/resource-center/case-studies/edms-consultants/</t>
   </si>
   <si>
     <t>resource-center/case-studies/farming-maintenance.report.json</t>
@@ -501,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -593,10 +608,10 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -605,21 +620,21 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
@@ -638,6 +653,32 @@
       </c>
       <c r="H5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-case-study-page.report.xlsx
+++ b/tools/importer/reports/import-case-study-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>_reportFile</t>
   </si>
@@ -113,6 +113,24 @@
   </si>
   <si>
     <t>https://fiixsoftware.com/resource-center/case-studies/farming-maintenance/</t>
+  </si>
+  <si>
+    <t>resource-center/case-studies/scotts-miracle-gro.report.json</t>
+  </si>
+  <si>
+    <t>["hero-case-study","case-study-intro-components","columns-media","hero-cta"]</t>
+  </si>
+  <si>
+    <t>resource-center/case-studies/scotts-miracle-gro</t>
+  </si>
+  <si>
+    <t>2026-08-19T10:11:05.372Z</t>
+  </si>
+  <si>
+    <t>How Fiix CMMS Improved Maintenance Ops at Scotts Miracle-Gro | Fiix</t>
+  </si>
+  <si>
+    <t>https://fiixsoftware.com/resource-center/case-studies/scotts-miracle-gro/</t>
   </si>
   <si>
     <t>resource-center/case-studies/universal-pure.report.json</t>
@@ -516,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -660,10 +678,10 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -672,13 +690,39 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
